--- a/qa/Research-Oyster-QA.xlsx
+++ b/qa/Research-Oyster-QA.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature tracker'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature tracker'!$A$1:$G$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,11 +34,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000F766E"/>
+      <color rgb="005B5B6B"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001E7A34"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F766E"/>
     </font>
     <font>
       <b val="1"/>
@@ -77,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -97,7 +101,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,15 +470,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,6 +513,11 @@
           <t>Result / found &amp; fixed</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>How verified (this pass · 2026-08-07)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -529,12 +542,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>PASS (fixed)</t>
+          <t>REVIEWED</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Reviewed. Fixed the branch trap: header defaulted to main while docs use the Studio branch — added the OYSTER_BRANCH example to the header.</t>
+          <t>Branch-trap defect found + fixed by inspection (header defaulted to main; added the OYSTER_BRANCH example). The end-to-end from-scratch install is NOT executed — it installs system packages and would modify this host.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Code review only — not run from scratch (would modify the host).</t>
         </is>
       </c>
     </row>
@@ -566,7 +584,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Self-healing launcher verified by code + live run.</t>
+          <t>Self-healing launcher. Ran ./studio live: '✓ database ready · ✓ signed in to Claude · ✓ starting…'.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Ran ./studio live 2026-08-07.</t>
         </is>
       </c>
     </row>
@@ -601,6 +624,11 @@
           <t>auth pill shows ambient/token; ./studio runs claude auth login if a CLI exists.</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>auth pill confirmed live (SB1); the pre-sign-in branch by code review.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -623,14 +651,19 @@
           <t>a clear message, not a stack trace</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Was an uvicorn traceback. Now pre-binds the port and prints a friendly 'already running' message + how to stop it. Re-tested live.</t>
+          <t>Was an uvicorn traceback. Now pre-binds the port and prints a friendly 'already running' message + how to stop it.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ran ./studio live 2026-08-07 with 8770 busy → friendly message + exit 1.</t>
         </is>
       </c>
     </row>
@@ -665,6 +698,11 @@
           <t>'auth: ambient · db: ok' rendered.</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 2026-08-07: pill read 'auth: ambient · db: ok'.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -694,7 +732,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Verified via Playwright: input enabled.</t>
+          <t>Input enables on new conversation.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 2026-08-07: input enabled after '+ New research'.</t>
         </is>
       </c>
     </row>
@@ -719,14 +762,19 @@
           <t>the chosen one activates; its stream/report reload; SSE reconnects</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>openConversation resets panes + reopens EventSource.</t>
+          <t>openConversation resets panes + reopens EventSource. Conversations live in server memory, so the list resets on a server restart; finished reports persist and are reachable via the Reports sidebar (SB4).</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 2026-08-07: opened conversations; in-memory-only limitation confirmed by code + a restart.</t>
         </is>
       </c>
     </row>
@@ -758,7 +806,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25 reports listed; doc view iframe → /api/report/{id}; Back works.</t>
+          <t>27 reports listed; doc view iframe → /api/report/{id}; Back works. Restart-proof path to any finished report.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 2026-08-07: opened job 1861 in doc view — real POV rendered, 0 console errors.</t>
         </is>
       </c>
     </row>
@@ -790,7 +843,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12 key fields shown; presence-only; verified.</t>
+          <t>12 key fields; presence-only.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 2026-08-07: 12 key fields shown.</t>
         </is>
       </c>
     </row>
@@ -822,7 +880,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Validated on Meridian + Voltline live runs.</t>
+          <t>The Ninja Creami brief typed in the UI started a real run.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run 2026-08-07 (job 1861) — sent via the UI, ran to a finished report.</t>
         </is>
       </c>
     </row>
@@ -857,6 +920,11 @@
           <t>thinking_start/thinking events render token-by-token.</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run: 27 thinking events in the stream.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -889,6 +957,11 @@
           <t>text deltas stream.</t>
         </is>
       </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run: 89 text deltas in the stream.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -918,7 +991,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>result/done events verified.</t>
+          <t>done event fires; input re-enables.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run: 'done' events emitted; cost/re-enable path by code.</t>
         </is>
       </c>
     </row>
@@ -950,7 +1028,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Verified when synthesis failed earlier — error event shown, not swallowed.</t>
+          <t>Errors are emitted to the feed as 'type(exc).__name__: exc', not swallowed.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run: a search_web tool error surfaced in the feed (is_error) — real, not a euphemism.</t>
         </is>
       </c>
     </row>
@@ -975,14 +1058,19 @@
           <t>no hang/duplicate; defined behavior</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Today: blocked with a clear 409. Chat-while-working is the planned v1.1 upgrade.</t>
+          <t>Today: input is disabled during a run, and the send endpoint returns a clear 409 as a backstop. Chat-while-working is the planned v1.1 upgrade.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>409-on-busy by code (studio.py:489) + input-disable in send(); not re-driven via an authed send this pass.</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1102,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Verified on live runs.</t>
+          <t>Every tool call + result renders; expandable.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run: 75 tool calls / 76 results streamed to the feed.</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1139,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Validated on Meridian + Voltline.</t>
+          <t>Nodes update live, including the review→re-collect loop.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run: full timeline observed plan→discover→collect→quantify→synthesize→review(loop)→verify→export.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1176,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>source_runs + feed show real outcomes.</t>
+          <t>Real outcomes shown.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>LIVE creami run: search_web returned is_error:true 'Error executing tool' — surfaced honestly in the feed.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1198,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>I open the Report tab after a run</t>
+          <t>I open the Report/doc view after a run</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1110,7 +1213,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>pov/glance/[n] markers present; iframe loads.</t>
+          <t>POV/at-a-glance/[n] all render.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 2026-08-07: job 1861 rendered in the doc view — 'The wedge is trust, not texture', at-a-glance + [n] present, 0 console errors.</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1243,19 @@
           <t>docx/deck/HTML/Sources/README/CSV each download</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>All chips 200 w/ correct MIME. Fixed a race that duplicated chips (21→7).</t>
+          <t>All chips 200 w/ correct MIME. (Earlier fixed a race that duplicated chips 21→7.)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Wire 2026-08-07: /api/report/1861/files → 7 chips with correct labels/MIME.</t>
         </is>
       </c>
     </row>
@@ -1167,14 +1280,19 @@
           <t>formatted Word: title, POV, at-a-glance, tables, themes, sources</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Validated (Voltline).</t>
+          <t>Fixed gaming-specific 'What players are saying' heading → 'What people are saying' (this tool is vertical-agnostic). Re-exported clean.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Grader 2026-08-07: docx opens (34 KB doc.xml), has text, heading now neutral, no 'players'.</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1324,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Validated.</t>
+          <t>9-slide deck built.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Grader 2026-08-07: deck.pptx opens with 9 slides.</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1361,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19 deep-link entries on Voltline.</t>
+          <t>Numbered [n] ledger with deep links, tool provenance, and the supporting quote.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Read the file 2026-08-07: 16 [n] entries, e.g. [1] r/ninjacreami with the burning-blade quote + URL.</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1391,19 @@
           <t>charts as PNG+SVG+CSV; raw-data per connector + evidence.json</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Files present. Fixed the 'Charts (folder)' chip: was a 400 text, now downloads a zip.</t>
+          <t>Files present. (Earlier fixed the 'Charts (folder)' chip: 400 → zip.)</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Grader 2026-08-07: 6 chart files + 4 raw-data files for job 1861.</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1435,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Voltline validated: no jargon/'n=', scannable.</t>
+          <t>POV takes a position that disagrees with the brief ('trust, not texture'); action-title themes; plain voice; real counts (6 of 10 threads); triangulated vs Wirecutter.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Read the synthesis + grader 2026-08-07: 0 banned jargon, 23 real numbers, action titles.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1472,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Verified.</t>
+          <t>db+auth only, no secret-looking values.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Wire 2026-08-07: keys=[db,auth,mcp_python…]; no secret pattern in body.</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1509,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>configured map only; no values.</t>
+          <t>presence map only.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Wire 2026-08-07: all values booleans; no raw secret strings.</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1546,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Verified by code + Step-1 tests.</t>
+          <t>Round-trip preserves DB + token; blank keeps.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Wire 2026-08-07: POST w/ token → configured:true, .env 0600, DATABASE_URL intact, no-token POST → 403, restored.</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1583,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Traversal → 404.</t>
+          <t>Traversal + non-allow-listed names refused.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Wire 2026-08-07: ../etc/passwd → 404, encoded traversal → 404, .env → 404.</t>
         </is>
       </c>
     </row>
@@ -1452,17 +1610,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>graceful message, not a 500</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+          <t>graceful message, not a 500 or dev jargon</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Missing job returned a 500. Now returns a graceful 404 (missing) / 409 (no synthesis yet). Re-tested.</t>
+          <t>Missing job → 404. NEW FIX: an unsynthesized/still-running job used to render a 409 body that leaked 'The agent must call write_research_synthesis' + a raw exception. Now a calm 200 'your report is being prepared' page — no tool names, no stack trace.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Wire 2026-08-07: job 99999999 → 404; unsynthesized job 1894 → 200 + 'being prepared', 0 jargon.</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1657,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Replay verified (dumped full transcript earlier).</t>
+          <t>Replay then live-tail.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Wire 2026-08-07: replayed 284 events with correct types (text/tool/thinking/node/job_linked).</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1679,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Any page load</t>
+          <t>Any page load / opening a mid-run report</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1519,14 +1687,19 @@
           <t>no console errors</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Was a /favicon.ico 404 on every load. Added an inline data-URI favicon; console errors now 0.</t>
+          <t>Earlier fixed a favicon 404. NEW FIX: opening the Report tab while a run was still going logged two 409s (report + files not ready). The report-pending page now returns 200, so no console error mid-run.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Playwright 2026-08-07: 0 console errors on load AND on opening a finished report (was 2×409 mid-run before the fix).</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1724,7 @@
           <t>separate legacy app; runs the gaming pipeline + browser-capture pairing</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
@@ -1559,6 +1732,11 @@
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Distinct from the Studio (8770). Legacy 'two products in one repo' — works, but out of the Studio demo path.</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Not exercised this pass — out of the Studio demo path.</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1761,7 @@
           <t>extension pairs with the Control Center (8765), not the Studio</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
@@ -1591,6 +1769,11 @@
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Demoted fallback path; server-side collection is primary. Real provenance bugs in the extension are v2 (audit #4).</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Not exercised this pass — fallback path, not in the demo.</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1798,7 @@
           <t>two settings UIs own disjoint .env keys</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
@@ -1623,6 +1806,11 @@
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Studio keys modal (12 research keys) vs Control Center Setup (DB+streaming). For the Studio, DATABASE_URL is set by the installer, so not a blocker.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Studio keys modal verified live (E3); the split confirmed by code.</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1835,7 @@
           <t>the postgres acceptance scripts are collected</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>DEFER</t>
         </is>
@@ -1657,9 +1845,14 @@
           <t>They're standalone __main__ scripts, not pytest — not collected. Real hygiene gap; wiring risks a flaky red step pre-demo. Post-demo fix.</t>
         </is>
       </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed by code review this pass; deliberately deferred to post-demo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:G37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1670,19 +1863,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -1705,7 +1898,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1715,7 +1908,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -1728,10 +1921,103 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REVIEWED</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Total stories: 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>How to read this tracker (2026-08-07 pass):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PASS          — exercised from the human surface this pass; works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PASS (fixed)  — a real defect was found and fixed; re-tested from the surface this pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REVIEWED      — read the code this pass but did NOT execute end-to-end (see the last column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NOTE          — works, with a known limitation worth flagging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DEFER         — real gap, deliberately deferred post-demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>The last column names the exact evidence behind each verdict TODAY — a live run, a wire</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>test, a Playwright drive, or code review only. The anchor is a fresh end-to-end run through</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>the real UI: a Ninja Creami competitor brief → finished report (job 1861). That run also</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>surfaced 3 real defects, now fixed: E5 (report jargon page), R3/R7 (gaming language in</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>reports), UX1 (409s when opening a mid-run report).</t>
         </is>
       </c>
     </row>

--- a/qa/Research-Oyster-QA.xlsx
+++ b/qa/Research-Oyster-QA.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature tracker'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature tracker'!$A$1:$G$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -547,12 +547,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Branch-trap defect found + fixed by inspection (header defaulted to main; added the OYSTER_BRANCH example). The end-to-end from-scratch install is NOT executed — it installs system packages and would modify this host.</t>
+          <t>Branch-trap defect found + fixed by inspection (header defaulted to main; added the OYSTER_BRANCH example). The end-to-end from-scratch install is NOT executed — it installs system packages and would modify/consume disk on this host.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Code review only — not run from scratch (would modify the host).</t>
+          <t>Syntax-validated (bash -n) 2026-08-07 + code review. NOT run from scratch (installs system packages, risks host/disk).</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>409-on-busy by code (studio.py:489) + input-disable in send(); not re-driven via an authed send this pass.</t>
+          <t>LIVE 2026-08-07: during a run the input + send button were disabled, and a programmatic send returned 409 — no hang, no duplicate.</t>
         </is>
       </c>
     </row>
@@ -1203,22 +1203,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>designed HTML renders inline; per-job dropdown</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>designed HTML renders inline; per-job dropdown; a real title (not 'internal')</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>POV/at-a-glance/[n] all render.</t>
+          <t>POV/at-a-glance/[n] all render. NEW FIX: the report title was 'internal' — a brief that opens with '# Research brief — internal' collapsed to the label. Now uses the first real sentence across HTML/deck/docx.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Playwright 2026-08-07: job 1861 rendered in the doc view — 'The wedge is trust, not texture', at-a-glance + [n] present, 0 console errors.</t>
+          <t>Playwright 2026-08-07: job 1861 rendered in the doc view — real title, 'The wedge is trust, not texture', at-a-glance + [n], 0 console errors.</t>
         </is>
       </c>
     </row>
@@ -1317,19 +1317,19 @@
           <t>16:9 deck: title, POV, stat tiles, charts, recs, sources</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9-slide deck built.</t>
+          <t>9-slide deck: POV, executive answer, 2 chart slides, action-title themes, recs, method, numbered sources. NEW FIX: slide-1 title used the raw brief — now the clean report title.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Grader 2026-08-07: deck.pptx opens with 9 slides.</t>
+          <t>Extracted every slide 2026-08-07: 9 slides, correct order, charts embedded, clean title, no jargon.</t>
         </is>
       </c>
     </row>
@@ -1669,190 +1669,301 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>UX1</t>
+          <t>AP1</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Whole app</t>
+          <t>Data/keys</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Any page load / opening a mid-run report</t>
+          <t>I enter my Apify token in ⚙ API keys</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>no console errors</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>PASS (fixed)</t>
+          <t>token persists to .env (0600); the app reports it configured; the MCP run picks it up</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Earlier fixed a favicon 404. NEW FIX: opening the Report tab while a run was still going logged two 409s (report + files not ready). The report-pending page now returns 200, so no console error mid-run.</t>
+          <t>The exact flow to turn Apify on for the demo.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Playwright 2026-08-07: 0 console errors on load AND on opening a finished report (was 2×409 mid-run before the fix).</t>
+          <t>Playwright 2026-08-07: typed a token in the modal → saved → .env 0600 → /api/settings configured:true (fake token removed after).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>AP2</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Control Center</t>
+          <t>Data/keys</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>I use the 8765 dashboard (Gaming Pulse + capture pairing)</t>
+          <t>My Apify key is wrong/expired or out of credits mid-run</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>separate legacy app; runs the gaming pipeline + browser-capture pairing</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>NOTE</t>
+          <t>the run degrades to free sources with a plain-English reason — never crashes</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Distinct from the Studio (8770). Legacy 'two products in one repo' — works, but out of the Studio demo path.</t>
+          <t>NEW FIX: a bad key raised a raw 401 HTTPStatusError (would thrash a live run). Now both Apify paths catch 401/402/403/429/timeout and return a soft fallback with the reason + next step, exactly like a missing key.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Not exercised this pass — out of the Studio demo path.</t>
+          <t>LIVE 2026-08-07: empty key → graceful not_configured; bad key → 'Apify rejected the token (HTTP 401)… falling back to free sources', routed to Reddit, no crash. Unit-tested.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>AP3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Browser extension</t>
+          <t>Data/keys</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>I capture from a page via the extension</t>
+          <t>I run with NO paid keys at all</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>extension pairs with the Control Center (8765), not the Studio</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>NOTE</t>
+          <t>still produces a confident report from free sources (Reddit/web), looping when signal is thin</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Demoted fallback path; server-side collection is primary. Real provenance bugs in the extension are v2 (audit #4).</t>
+          <t>Free connectors carry a run end-to-end.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Not exercised this pass — fallback path, not in the demo.</t>
+          <t>LIVE 2026-08-07: the Creami run (no keys) completed to a full report; the review gate looped to collect more on thin signal.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>UX1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Settings split</t>
+          <t>Whole app</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>I set keys from the UI</t>
+          <t>Any page load / opening a mid-run report</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>two settings UIs own disjoint .env keys</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>NOTE</t>
+          <t>no console errors</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Studio keys modal (12 research keys) vs Control Center Setup (DB+streaming). For the Studio, DATABASE_URL is set by the installer, so not a blocker.</t>
+          <t>Earlier fixed a favicon 404. NEW FIX: opening the Report tab while a run was still going logged two 409s (report + files not ready). The report-pending page now returns 200, so no console error mid-run.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Studio keys modal verified live (E3); the split confirmed by code.</t>
+          <t>Playwright 2026-08-07: 0 console errors on load AND on opening a finished report (was 2×409 mid-run before the fix).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Control Center</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>I use the 8765 dashboard (Gaming Pulse + capture pairing)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>separate legacy app; runs the gaming pipeline + browser-capture pairing</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Distinct from the Studio (8770). Legacy 'two products in one repo' — works, but out of the Studio demo path.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Launched live 2026-08-07: GET / → 200 'Research Oyster' with pairing/setup UI; /api/status → 200. Not part of the Studio demo path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Browser extension</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>I capture from a page via the extension</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>extension pairs with the Control Center (8765), not the Studio</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Demoted fallback path; server-side collection is primary. Real provenance bugs in the extension are v2 (audit #4).</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Not exercised this pass — fallback path, not in the demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Settings split</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>I set keys from the UI</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>two settings UIs own disjoint .env keys</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Studio keys modal (12 research keys) vs Control Center Setup (DB+streaming). For the Studio, DATABASE_URL is set by the installer, so not a blocker.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Studio keys modal verified live (E3); the split confirmed by code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>The test suite runs in CI</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>the postgres acceptance scripts are collected</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>DEFER</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>They're standalone __main__ scripts, not pytest — not collected. Real hygiene gap; wiring risks a flaky red step pre-demo. Post-demo fix.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Confirmed by code review this pass; deliberately deferred to post-demo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37"/>
+  <autoFilter ref="A1:G40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1863,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1918,7 +2029,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1934,7 +2045,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Total stories: 36</t>
+          <t>Total stories: 39</t>
         </is>
       </c>
     </row>
@@ -1996,28 +2107,63 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>test, a Playwright drive, or code review only. The anchor is a fresh end-to-end run through</t>
+          <t>test, a Playwright drive, or code review only. The anchor is fresh end-to-end runs through</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>the real UI: a Ninja Creami competitor brief → finished report (job 1861). That run also</t>
+          <t>the real UI (a Ninja Creami brief → report job 1861; an AirPods brief live). Those runs +</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>surfaced 3 real defects, now fixed: E5 (report jargon page), R3/R7 (gaming language in</t>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>the surface tests found 5 real defects, all now fixed and re-tested:</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>reports), UX1 (409s when opening a mid-run report).</t>
+          <t xml:space="preserve">  • E5/UX1 — the Report tab leaked 'write_research_synthesis' + a stack trace, and logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    409s, when opened mid-run → calm 200 'being prepared' page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • R3/R7 — gaming language ('What players are saying') on a kitchen report → neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • R1/R4 — every deliverable was titled 'internal' → clean title from the first sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • AP2 — a wrong/expired/credit-exhausted Apify key CRASHED the run (raw 401) → degrades</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    to free sources with a plain reason. This is the big demo-safety fix.</t>
         </is>
       </c>
     </row>

--- a/qa/Research-Oyster-QA.xlsx
+++ b/qa/Research-Oyster-QA.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature tracker'!$A$1:$G$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Feature tracker'!$A$1:$G$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1447,44 +1447,44 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>CW1</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Endpoint</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>The page checks health</t>
+          <t>I read a finding — is it weighted by how many people agree?</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>/api/health returns db+auth, no secrets</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>the report leads with what the crowd most ENDORSES (aggregate upvotes/likes/shares), not raw mention count; cites the endorsement</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>db+auth only, no secret-looking values.</t>
+          <t>NEW: a comment is worth the people behind it. patterns.weighted_consensus reads engagement from every metadata shape (incl. the Reddit top-level keys the metrics layer was dropping), ranks by conviction (shares&gt;upvotes&gt;comments, views damped, dislikes subtract), and the synthesis leads with it. Types-of-comments sentiment is the staged fast-follow.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Wire 2026-08-07: keys=[db,auth,mcp_python…]; no secret pattern in body.</t>
+          <t>LIVE run job 2102 (2026-08-07): report cites '176 upvotes', '65 upvotes', 'top-voted'; analyze_chatter called 10x; 24/58 rows carried engagement. Unit-tested.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>I view my saved keys</t>
+          <t>The page checks health</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>/api/settings GET returns presence only, never secrets</t>
+          <t>/api/health returns db+auth, no secrets</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1509,19 +1509,19 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>presence map only.</t>
+          <t>db+auth only, no secret-looking values.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Wire 2026-08-07: all values booleans; no raw secret strings.</t>
+          <t>Wire 2026-08-07: keys=[db,auth,mcp_python…]; no secret pattern in body.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>I save keys</t>
+          <t>I view my saved keys</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>POST writes .env 0600; blank keeps; DB/auth token preserved</t>
+          <t>/api/settings GET returns presence only, never secrets</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Round-trip preserves DB + token; blank keeps.</t>
+          <t>presence map only.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Wire 2026-08-07: POST w/ token → configured:true, .env 0600, DATABASE_URL intact, no-token POST → 403, restored.</t>
+          <t>Wire 2026-08-07: all values booleans; no raw secret strings.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>A file download is requested</t>
+          <t>I save keys</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>allow-listed; cannot traverse outside the job folder</t>
+          <t>POST writes .env 0600; blank keeps; DB/auth token preserved</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1583,19 +1583,19 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Traversal + non-allow-listed names refused.</t>
+          <t>Round-trip preserves DB + token; blank keeps.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Wire 2026-08-07: ../etc/passwd → 404, encoded traversal → 404, .env → 404.</t>
+          <t>Wire 2026-08-07: POST w/ token → configured:true, .env 0600, DATABASE_URL intact, no-token POST → 403, restored.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1605,34 +1605,34 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>I open a report for a missing/unsynthesized job</t>
+          <t>A file download is requested</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>graceful message, not a 500 or dev jargon</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>PASS (fixed)</t>
+          <t>allow-listed; cannot traverse outside the job folder</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Missing job → 404. NEW FIX: an unsynthesized/still-running job used to render a 409 body that leaked 'The agent must call write_research_synthesis' + a raw exception. Now a calm 200 'your report is being prepared' page — no tool names, no stack trace.</t>
+          <t>Traversal + non-allow-listed names refused.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Wire 2026-08-07: job 99999999 → 404; unsynthesized job 1894 → 200 + 'being prepared', 0 jargon.</t>
+          <t>Wire 2026-08-07: ../etc/passwd → 404, encoded traversal → 404, .env → 404.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1642,49 +1642,49 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>My browser reconnects to the stream</t>
+          <t>I open a report for a missing/unsynthesized job</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>/api/chat/stream?from= replays missed transcript then live-tails</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>graceful message, not a 500 or dev jargon</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Replay then live-tail.</t>
+          <t>Missing job → 404. NEW FIX: an unsynthesized/still-running job used to render a 409 body that leaked 'The agent must call write_research_synthesis' + a raw exception. Now a calm 200 'your report is being prepared' page — no tool names, no stack trace.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Wire 2026-08-07: replayed 284 events with correct types (text/tool/thinking/node/job_linked).</t>
+          <t>Wire 2026-08-07: job 99999999 → 404; unsynthesized job 1894 → 200 + 'being prepared', 0 jargon.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AP1</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Data/keys</t>
+          <t>Endpoint</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>I enter my Apify token in ⚙ API keys</t>
+          <t>My browser reconnects to the stream</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>token persists to .env (0600); the app reports it configured; the MCP run picks it up</t>
+          <t>/api/chat/stream?from= replays missed transcript then live-tails</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1694,19 +1694,19 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>The exact flow to turn Apify on for the demo.</t>
+          <t>Replay then live-tail.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Playwright 2026-08-07: typed a token in the modal → saved → .env 0600 → /api/settings configured:true (fake token removed after).</t>
+          <t>Wire 2026-08-07: replayed 284 events with correct types (text/tool/thinking/node/job_linked).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AP2</t>
+          <t>AP1</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1716,34 +1716,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>My Apify key is wrong/expired or out of credits mid-run</t>
+          <t>I enter my Apify token in ⚙ API keys</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>the run degrades to free sources with a plain-English reason — never crashes</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>PASS (fixed)</t>
+          <t>token persists to .env (0600); the app reports it configured; the MCP run picks it up</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>NEW FIX: a bad key raised a raw 401 HTTPStatusError (would thrash a live run). Now both Apify paths catch 401/402/403/429/timeout and return a soft fallback with the reason + next step, exactly like a missing key.</t>
+          <t>The exact flow to turn Apify on for the demo.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>LIVE 2026-08-07: empty key → graceful not_configured; bad key → 'Apify rejected the token (HTTP 401)… falling back to free sources', routed to Reddit, no crash. Unit-tested.</t>
+          <t>Playwright 2026-08-07: typed a token in the modal → saved → .env 0600 → /api/settings configured:true (fake token removed after).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AP3</t>
+          <t>AP2</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1753,123 +1753,123 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>I run with NO paid keys at all</t>
+          <t>My Apify key is wrong/expired or out of credits mid-run</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>still produces a confident report from free sources (Reddit/web), looping when signal is thin</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>the run degrades to free sources with a plain-English reason — never crashes</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Free connectors carry a run end-to-end.</t>
+          <t>NEW FIX: a bad key raised a raw 401 HTTPStatusError (would thrash a live run). Now both Apify paths catch 401/402/403/429/timeout and return a soft fallback with the reason + next step, exactly like a missing key.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>LIVE 2026-08-07: the Creami run (no keys) completed to a full report; the review gate looped to collect more on thin signal.</t>
+          <t>LIVE 2026-08-07: empty key → graceful not_configured; bad key → 'Apify rejected the token (HTTP 401)… falling back to free sources', routed to Reddit, no crash. Unit-tested.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>UX1</t>
+          <t>AP3</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Whole app</t>
+          <t>Data/keys</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Any page load / opening a mid-run report</t>
+          <t>I run with NO paid keys at all</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>no console errors</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>PASS (fixed)</t>
+          <t>still produces a confident report from free sources (Reddit/web), looping when signal is thin</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Earlier fixed a favicon 404. NEW FIX: opening the Report tab while a run was still going logged two 409s (report + files not ready). The report-pending page now returns 200, so no console error mid-run.</t>
+          <t>Free connectors carry a run end-to-end.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Playwright 2026-08-07: 0 console errors on load AND on opening a finished report (was 2×409 mid-run before the fix).</t>
+          <t>LIVE 2026-08-07: the Creami run (no keys) completed to a full report; the review gate looped to collect more on thin signal.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>UX1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Control Center</t>
+          <t>Whole app</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>I use the 8765 dashboard (Gaming Pulse + capture pairing)</t>
+          <t>Any page load / opening a mid-run report</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>separate legacy app; runs the gaming pipeline + browser-capture pairing</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>NOTE</t>
+          <t>no console errors</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>PASS (fixed)</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Distinct from the Studio (8770). Legacy 'two products in one repo' — works, but out of the Studio demo path.</t>
+          <t>Earlier fixed a favicon 404. NEW FIX: opening the Report tab while a run was still going logged two 409s (report + files not ready). The report-pending page now returns 200, so no console error mid-run.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Launched live 2026-08-07: GET / → 200 'Research Oyster' with pairing/setup UI; /api/status → 200. Not part of the Studio demo path.</t>
+          <t>Playwright 2026-08-07: 0 console errors on load AND on opening a finished report (was 2×409 mid-run before the fix).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Browser extension</t>
+          <t>Control Center</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>I capture from a page via the extension</t>
+          <t>I use the 8765 dashboard (Gaming Pulse + capture pairing)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>extension pairs with the Control Center (8765), not the Studio</t>
+          <t>separate legacy app; runs the gaming pipeline + browser-capture pairing</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1879,34 +1879,34 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Demoted fallback path; server-side collection is primary. Real provenance bugs in the extension are v2 (audit #4).</t>
+          <t>Distinct from the Studio (8770). Legacy 'two products in one repo' — works, but out of the Studio demo path.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Not exercised this pass — fallback path, not in the demo.</t>
+          <t>Launched live 2026-08-07: GET / → 200 'Research Oyster' with pairing/setup UI; /api/status → 200. Not part of the Studio demo path.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Settings split</t>
+          <t>Browser extension</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>I set keys from the UI</t>
+          <t>I capture from a page via the extension</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>two settings UIs own disjoint .env keys</t>
+          <t>extension pairs with the Control Center (8765), not the Studio</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1916,54 +1916,91 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Studio keys modal (12 research keys) vs Control Center Setup (DB+streaming). For the Studio, DATABASE_URL is set by the installer, so not a blocker.</t>
+          <t>Demoted fallback path; server-side collection is primary. Real provenance bugs in the extension are v2 (audit #4).</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Studio keys modal verified live (E3); the split confirmed by code.</t>
+          <t>Not exercised this pass — fallback path, not in the demo.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Settings split</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>I set keys from the UI</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>two settings UIs own disjoint .env keys</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Studio keys modal (12 research keys) vs Control Center Setup (DB+streaming). For the Studio, DATABASE_URL is set by the installer, so not a blocker.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Studio keys modal verified live (E3); the split confirmed by code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>The test suite runs in CI</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>the postgres acceptance scripts are collected</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>DEFER</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>They're standalone __main__ scripts, not pytest — not collected. Real hygiene gap; wiring risks a flaky red step pre-demo. Post-demo fix.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Confirmed by code review this pass; deliberately deferred to post-demo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G40"/>
+  <autoFilter ref="A1:G41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1974,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2029,7 +2066,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2045,7 +2082,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Total stories: 39</t>
+          <t>Total stories: 40</t>
         </is>
       </c>
     </row>
@@ -2107,63 +2144,105 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>test, a Playwright drive, or code review only. The anchor is fresh end-to-end runs through</t>
+          <t>test, a Playwright drive, or code review only. The definitive anchor is a FRESH end-to-end</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>the real UI (a Ninja Creami brief → report job 1861; an AirPods brief live). Those runs +</t>
+          <t>run through the real UI on current code (a Breville Barista Express brief → report job 2102),</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>the surface tests found 5 real defects, all now fixed and re-tested:</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>plus earlier runs (Creami 1861, AirPods) and the surface tests. Six real defects found this</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • E5/UX1 — the Report tab leaked 'write_research_synthesis' + a stack trace, and logged</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>pass, all fixed and re-verified in a fresh run:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    409s, when opened mid-run → calm 200 'being prepared' page.</t>
+          <t xml:space="preserve">  • E5/UX1 — the Report tab leaked 'write_research_synthesis' + a stack trace, and logged</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • R3/R7 — gaming language ('What players are saying') on a kitchen report → neutral.</t>
+          <t xml:space="preserve">    409s, when opened mid-run → calm 200 'being prepared' page.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • R1/R4 — every deliverable was titled 'internal' → clean title from the first sentence.</t>
+          <t xml:space="preserve">  • R3/R7 — gaming language ('What players are saying') on a kitchen report → neutral.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • AP2 — a wrong/expired/credit-exhausted Apify key CRASHED the run (raw 401) → degrades</t>
+          <t xml:space="preserve">  • R1/R4 — every deliverable was titled 'internal' → clean title from the first sentence.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    to free sources with a plain reason. This is the big demo-safety fix.</t>
+          <t xml:space="preserve">  • AP2 — a wrong/expired/credit-exhausted Apify key CRASHED the run (raw 401) → degrades</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    to free sources with a plain reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • MCP reap — a killed Studio orphaned its MCP server, so fresh runs silently used STALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    code (this was defeating the fixes above); now reaped on startup. THE sneaky one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • CW1 — findings were counted by mention, not weighted by endorsement; now the report</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    leads with consensus (upvotes/shares), the feature added this pass because it changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    the answer, not the polish.</t>
         </is>
       </c>
     </row>

--- a/qa/Research-Oyster-QA.xlsx
+++ b/qa/Research-Oyster-QA.xlsx
@@ -8566,14 +8566,14 @@
           <t>OYSTER_REPO/BRANCH/HOME</t>
         </is>
       </c>
-      <c r="E253" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>code+syntax; not run from scratch (modifies host)</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8598,14 +8598,14 @@
           <t>macos/linux/refuse</t>
         </is>
       </c>
-      <c r="E254" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8630,14 +8630,14 @@
           <t>sudo or die</t>
         </is>
       </c>
-      <c r="E255" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8662,14 +8662,14 @@
           <t>die if absent (mac)</t>
         </is>
       </c>
-      <c r="E256" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8694,14 +8694,14 @@
           <t>install if missing</t>
         </is>
       </c>
-      <c r="E257" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8726,14 +8726,14 @@
           <t>branch --depth 1</t>
         </is>
       </c>
-      <c r="E258" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8790,14 +8790,14 @@
           <t>install if missing</t>
         </is>
       </c>
-      <c r="E260" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8822,14 +8822,14 @@
           <t>install if missing</t>
         </is>
       </c>
-      <c r="E261" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8854,14 +8854,14 @@
           <t>pg_isready loop or die</t>
         </is>
       </c>
-      <c r="E262" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8886,14 +8886,14 @@
           <t>create role for OS user</t>
         </is>
       </c>
-      <c r="E263" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8918,14 +8918,14 @@
           <t>untouched if exists</t>
         </is>
       </c>
-      <c r="E264" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8950,14 +8950,14 @@
           <t>venv + requirements</t>
         </is>
       </c>
-      <c r="E265" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -8982,14 +8982,14 @@
           <t>venv-studio</t>
         </is>
       </c>
-      <c r="E266" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -9014,14 +9014,14 @@
           <t>defaults, 0600, never clobber</t>
         </is>
       </c>
-      <c r="E267" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -9078,14 +9078,14 @@
           <t>claude/codex mcp add</t>
         </is>
       </c>
-      <c r="E269" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -9110,14 +9110,14 @@
           <t>double-click icon</t>
         </is>
       </c>
-      <c r="E270" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -9142,14 +9142,14 @@
           <t>next steps printed</t>
         </is>
       </c>
-      <c r="E271" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -9174,14 +9174,14 @@
           <t>if signed in</t>
         </is>
       </c>
-      <c r="E272" s="6" t="inlineStr">
-        <is>
-          <t>REVIEWED</t>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>live: install.sh run from scratch 2026-08-07 — clone→venvs→deps→migrate→MCP attach, EXIT=0, imports ok</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8">
